--- a/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/listExercises-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/controller/__tests__/bbt/exercise-controller/listExercises-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="96">
-  <si>
-    <t>Statement: exercise-controller.listExercises(options?) – Server Action. No input validation. Delegates to exerciseService.listExercises(). Returns ActionResult&lt;PageResult&lt;Exercise&gt;&gt;.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="315" uniqueCount="150">
+  <si>
+    <t>Statement: listExercises(options?) – Retrieves a paginated list of exercises and returns an ActionResult&lt;PageResult&lt;Exercise&gt;&gt;. options is fully optional; when omitted, only active exercises are returned. includeInactive: false returns only active exercises; includeInactive: true returns all exercises. muscleGroup filters results to the specified group. search filters results by name. page and pageSize control pagination; when omitted, defaults apply. Returns a failure with the service error message for AppError.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: ExerciseListOptions? { search?, muscleGroup?, includeInactive?, page?, pageSize? }</t>
+    <t>Input: options?: ExerciseListOptions { includeInactive?: boolean, muscleGroup?: MuscleGroup, search?: string, page?: number, pageSize?: number }</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>exerciseService.listExercises is mock-injected</t>
+    <t>Valid MuscleGroup values: CHEST, BACK, LEGS, SHOULDERS, ARMS, CORE. page: 0 and 1 both return the first page; page 2 returns the second page. pageSize: 0 returns no items; pageSize: 1 returns at most one item. search: undefined or empty string returns all exercises.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: ActionResult&lt;PageResult&lt;Exercise&gt;&gt;</t>
+    <t>Output: Promise&lt;ActionResult&lt;PageResult&lt;Exercise&gt;&gt;&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>On success: page returned. On AppError: failure. On error: generic failure.</t>
+    <t>On success: exercise list retrieved successfully, returned data matches the expected page result. On AppError: operation fails with the service error message.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -64,46 +64,43 @@
     <t>Invalid EC</t>
   </si>
   <si>
-    <t>no options</t>
-  </si>
-  <si>
-    <t>service resolves page</t>
-  </si>
-  <si>
-    <t>with search</t>
-  </si>
-  <si>
-    <t>search option passed to service</t>
-  </si>
-  <si>
-    <t>with muscleGroup</t>
-  </si>
-  <si>
-    <t>muscleGroup filter passed</t>
+    <t>options</t>
+  </si>
+  <si>
+    <t>options omitted → exercise list retrieved successfully, only active exercises returned</t>
   </si>
   <si>
     <t>includeInactive</t>
   </si>
   <si>
-    <t>flag passed to service</t>
-  </si>
-  <si>
-    <t>with pagination</t>
-  </si>
-  <si>
-    <t>pagination passed to service</t>
-  </si>
-  <si>
-    <t>service outcome</t>
-  </si>
-  <si>
-    <t>resolves page</t>
-  </si>
-  <si>
-    <t>throws AppError → failure</t>
-  </si>
-  <si>
-    <t>throws Error → generic failure</t>
+    <t>includeInactive: false → exercise list retrieved successfully, only active exercises returned</t>
+  </si>
+  <si>
+    <t>includeInactive: true → exercise list retrieved successfully, all exercises returned (active and inactive)</t>
+  </si>
+  <si>
+    <t>muscleGroup filter</t>
+  </si>
+  <si>
+    <t>muscleGroup: CHEST → exercise list retrieved successfully, returned items all have muscleGroup CHEST</t>
+  </si>
+  <si>
+    <t>search filter</t>
+  </si>
+  <si>
+    <t>search: "Bench" → exercise list retrieved successfully, returned items all contain "Bench" in their name</t>
+  </si>
+  <si>
+    <t>result ordering</t>
+  </si>
+  <si>
+    <t>two exercises exist → exercise list retrieved successfully, items returned in alphabetical order</t>
+  </si>
+  <si>
+    <t>Service error</t>
+  </si>
+  <si>
+    <t>An AppError occurs → operation fails with message "Service failed"</t>
   </si>
   <si>
     <t>No TC</t>
@@ -121,61 +118,67 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>no options, service resolves { items:[EXERCISE], total:1 }</t>
-  </si>
-  <si>
-    <t>{ success: true, data.total: 1 }</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>{ search: "Bench" }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; listExercises({ search:"Bench" }) called</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>{ muscleGroup: "CHEST" }, service resolves</t>
-  </si>
-  <si>
-    <t>{ success: true }; listExercises(options) called</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>{ includeInactive: true }, service resolves</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>{ page: 2, pageSize: 10 }, service resolves</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>no options, service throws AppError("Service error")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "Service error" }</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>no options, service throws Error("DB error")</t>
-  </si>
-  <si>
-    <t>{ success: false, message: "An unexpected error occurred" }</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>no options provided, the service returns a page of active exercises</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items contain only active exercises</t>
+  </si>
+  <si>
+    <t>Passed</t>
+  </si>
+  <si>
+    <t>EC-2</t>
+  </si>
+  <si>
+    <t>includeInactive: false, the service returns a page of active exercises</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>includeInactive: true, the service returns a page including inactive exercises</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items include all exercises</t>
+  </si>
+  <si>
+    <t>EC-4</t>
+  </si>
+  <si>
+    <t>muscleGroup: CHEST, the service returns exercises matching that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items all have muscleGroup CHEST</t>
+  </si>
+  <si>
+    <t>EC-5</t>
+  </si>
+  <si>
+    <t>search: "Bench", the service returns exercises whose name contains "Bench"</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items all contain "Bench" in their name</t>
+  </si>
+  <si>
+    <t>EC-6</t>
+  </si>
+  <si>
+    <t>no options provided, the service returns two exercises ordered alphabetically ("A Exercise", "B Exercise")</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items are in order: "A Exercise" then "B Exercise"</t>
+  </si>
+  <si>
+    <t>EC-7</t>
+  </si>
+  <si>
+    <t>no options provided, an AppError occurs</t>
+  </si>
+  <si>
+    <t>operation fails with message "Service failed"</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -184,19 +187,193 @@
     <t>BVA Test Case</t>
   </si>
   <si>
-    <t>includeInactive=false (default) → active only; includeInactive=true → all</t>
+    <t>search boundary</t>
+  </si>
+  <si>
+    <t>search: undefined → treated as no filter, service returns all exercises</t>
+  </si>
+  <si>
+    <t>search: "" (empty string) → treated as no filter, service returns all exercises</t>
+  </si>
+  <si>
+    <t>search: "a" (single character) → service returns exercises matching that character</t>
+  </si>
+  <si>
+    <t>muscleGroup enum</t>
+  </si>
+  <si>
+    <t>muscleGroup: CHEST → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: BACK → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: LEGS → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: SHOULDERS → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: ARMS → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>muscleGroup: CORE → service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>page boundary</t>
+  </si>
+  <si>
+    <t>page: 0 (below conventional first page) → service returns first page of results</t>
+  </si>
+  <si>
+    <t>page: 1 (first page) → service returns first page of results</t>
+  </si>
+  <si>
+    <t>page: 2 (second page, beyond available data) → service returns empty items list with total reflecting actual count</t>
+  </si>
+  <si>
+    <t>page: undefined → service applies default and returns first page of results</t>
+  </si>
+  <si>
+    <t>pageSize boundary</t>
+  </si>
+  <si>
+    <t>pageSize: 0 → service returns empty items list</t>
+  </si>
+  <si>
+    <t>pageSize: 1 → service returns at most one item</t>
+  </si>
+  <si>
+    <t>pageSize: undefined → service applies default page size and returns first page of results</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>includeInactive=true</t>
-  </si>
-  <si>
-    <t>{ includeInactive: true }</t>
-  </si>
-  <si>
-    <t>listExercises({ includeInactive:true }) called</t>
+    <t>BVA-1  (search=undef)</t>
+  </si>
+  <si>
+    <t>search: undefined, the service returns all exercises</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, total is 1, items has length 1</t>
+  </si>
+  <si>
+    <t>BVA-2  (search="")</t>
+  </si>
+  <si>
+    <t>search: "" (empty string), the service returns all exercises</t>
+  </si>
+  <si>
+    <t>BVA-3  (search="a")</t>
+  </si>
+  <si>
+    <t>search: "a" (single character), the service returns matching exercises</t>
+  </si>
+  <si>
+    <t>BVA-4  (mg=CHEST)</t>
+  </si>
+  <si>
+    <t>muscleGroup: CHEST, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is CHEST</t>
+  </si>
+  <si>
+    <t>BVA-5  (mg=BACK)</t>
+  </si>
+  <si>
+    <t>muscleGroup: BACK, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is BACK</t>
+  </si>
+  <si>
+    <t>BVA-6  (mg=LEGS)</t>
+  </si>
+  <si>
+    <t>muscleGroup: LEGS, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is LEGS</t>
+  </si>
+  <si>
+    <t>BVA-7  (mg=SHOULDERS)</t>
+  </si>
+  <si>
+    <t>muscleGroup: SHOULDERS, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is SHOULDERS</t>
+  </si>
+  <si>
+    <t>BVA-8  (mg=ARMS)</t>
+  </si>
+  <si>
+    <t>muscleGroup: ARMS, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is ARMS</t>
+  </si>
+  <si>
+    <t>BVA-9  (mg=CORE)</t>
+  </si>
+  <si>
+    <t>muscleGroup: CORE, the service returns exercises for that muscle group</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, returned items[0].muscleGroup is CORE</t>
+  </si>
+  <si>
+    <t>BVA-10 (page=0)</t>
+  </si>
+  <si>
+    <t>page: 0, the service returns the first page of results</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, items has length 1</t>
+  </si>
+  <si>
+    <t>BVA-11 (page=1)</t>
+  </si>
+  <si>
+    <t>page: 1, the service returns the first page of results</t>
+  </si>
+  <si>
+    <t>BVA-12 (page=2)</t>
+  </si>
+  <si>
+    <t>page: 2, the service returns an empty page because the data fits on page 1 (items: [], total: 1)</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, items has length 0, total is 1</t>
+  </si>
+  <si>
+    <t>BVA-13 (page=undef)</t>
+  </si>
+  <si>
+    <t>page: undefined, the service applies default and returns the first page of results</t>
+  </si>
+  <si>
+    <t>BVA-14 (pageSize=0)</t>
+  </si>
+  <si>
+    <t>pageSize: 0, the service returns an empty items list (items: [], total: 1)</t>
+  </si>
+  <si>
+    <t>exercise list retrieved successfully, items has length 0</t>
+  </si>
+  <si>
+    <t>BVA-15 (pageSize=1)</t>
+  </si>
+  <si>
+    <t>pageSize: 1, the service returns at most one item</t>
+  </si>
+  <si>
+    <t>BVA-16 (pageSize=undef)</t>
+  </si>
+  <si>
+    <t>pageSize: undefined, the service applies default page size and returns the first page of results</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -205,64 +382,52 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>EP-1</t>
-  </si>
-  <si>
-    <t>No options, service resolves</t>
-  </si>
-  <si>
-    <t>success=true, page returned</t>
-  </si>
-  <si>
-    <t>EP-2</t>
-  </si>
-  <si>
-    <t>With search filter</t>
-  </si>
-  <si>
-    <t>success=true, service called with options</t>
-  </si>
-  <si>
-    <t>EP-3</t>
-  </si>
-  <si>
-    <t>muscleGroup filter</t>
-  </si>
-  <si>
-    <t>EP-4</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>success=true, all exercises returned</t>
-  </si>
-  <si>
-    <t>EP-5</t>
-  </si>
-  <si>
-    <t>With pagination</t>
-  </si>
-  <si>
-    <t>success=true, service called with pagination</t>
-  </si>
-  <si>
-    <t>EP-6</t>
-  </si>
-  <si>
-    <t>Service throws AppError</t>
-  </si>
-  <si>
-    <t>success=false, message from error</t>
-  </si>
-  <si>
-    <t>EP-7</t>
-  </si>
-  <si>
-    <t>Service throws unexpected Error</t>
-  </si>
-  <si>
-    <t>success=false, "An unexpected error occurred"</t>
+    <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>BVA-4</t>
+  </si>
+  <si>
+    <t>BVA-5</t>
+  </si>
+  <si>
+    <t>BVA-6</t>
+  </si>
+  <si>
+    <t>BVA-7</t>
+  </si>
+  <si>
+    <t>BVA-8</t>
+  </si>
+  <si>
+    <t>BVA-9</t>
+  </si>
+  <si>
+    <t>BVA-10</t>
+  </si>
+  <si>
+    <t>BVA-11</t>
+  </si>
+  <si>
+    <t>BVA-12</t>
+  </si>
+  <si>
+    <t>BVA-13</t>
+  </si>
+  <si>
+    <t>BVA-14</t>
+  </si>
+  <si>
+    <t>BVA-15</t>
+  </si>
+  <si>
+    <t>BVA-16</t>
   </si>
   <si>
     <t>Testing</t>
@@ -295,16 +460,13 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>EXM-02/EXM-06</t>
+    <t>CTRL-17</t>
   </si>
   <si>
     <t>n/a</t>
   </si>
   <si>
     <t>not yet</t>
-  </si>
-  <si>
-    <t>-</t>
   </si>
 </sst>
 </file>
@@ -820,7 +982,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D8"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -875,10 +1037,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>20</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>1</v>
@@ -889,10 +1051,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>22</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>1</v>
@@ -903,10 +1065,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>24</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>1</v>
@@ -917,10 +1079,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="1" t="s">
         <v>25</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>26</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>1</v>
@@ -931,27 +1093,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D8" s="1" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="9" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -974,19 +1122,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -994,13 +1142,13 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>36</v>
       </c>
       <c r="E2" s="5" t="s">
         <v>36</v>
@@ -1017,10 +1165,10 @@
         <v>38</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1028,16 +1176,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="D4" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="D4" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1045,16 +1193,16 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>42</v>
-      </c>
       <c r="E5" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1068,10 +1216,10 @@
         <v>46</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1079,16 +1227,16 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1096,16 +1244,16 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>52</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1116,7 +1264,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C2"/>
+  <dimension ref="A1:C17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -1126,13 +1274,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -1140,10 +1288,175 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>55</v>
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="6" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="7" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="8" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="11" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="12" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>75</v>
       </c>
     </row>
   </sheetData>
@@ -1154,7 +1467,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E2"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1166,19 +1479,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>56</v>
+        <v>76</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1186,16 +1499,271 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>57</v>
+        <v>77</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>59</v>
+        <v>79</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>59</v>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>117</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1206,7 +1774,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:F24"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1219,22 +1787,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>119</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>120</v>
       </c>
       <c r="D1" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>32</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1242,19 +1810,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>62</v>
+        <v>33</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>63</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>64</v>
+        <v>35</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>64</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1262,19 +1830,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>65</v>
+        <v>37</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>66</v>
+        <v>38</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>67</v>
+        <v>35</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1282,19 +1850,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>68</v>
+        <v>39</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>69</v>
+        <v>40</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>67</v>
+        <v>41</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>67</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1302,19 +1870,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>70</v>
+        <v>42</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>71</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>72</v>
+        <v>44</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>72</v>
+        <v>36</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1322,19 +1890,19 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>74</v>
+        <v>46</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>75</v>
+        <v>47</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>75</v>
+        <v>36</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1342,19 +1910,19 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>76</v>
+        <v>48</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>1</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>77</v>
+        <v>49</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>78</v>
+        <v>36</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1362,19 +1930,339 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>121</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="E8" s="1" t="s">
+      <c r="F9" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D10" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F8" s="5" t="s">
-        <v>81</v>
+      <c r="E10" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="13" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D13" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="E13" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="1">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>126</v>
+      </c>
+      <c r="D14" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="E14" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="15" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="1">
+        <v>14</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>127</v>
+      </c>
+      <c r="D15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="E15" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="1">
+        <v>15</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="17" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="1">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="1">
+        <v>17</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>130</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="E18" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="19" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="1">
+        <v>18</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>131</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="E19" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1">
+        <v>19</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>132</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="1">
+        <v>20</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>133</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="22" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" s="1">
+        <v>21</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>134</v>
+      </c>
+      <c r="D22" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="E22" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="23" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="1">
+        <v>22</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="D23" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="E23" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" s="1">
+        <v>23</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="D24" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1402,16 +2290,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>83</v>
+        <v>138</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>84</v>
+        <v>139</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1419,45 +2307,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>85</v>
+        <v>140</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>90</v>
+        <v>145</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>91</v>
+        <v>146</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>86</v>
+        <v>141</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>92</v>
+      <c r="A3" s="1" t="s">
+        <v>147</v>
       </c>
       <c r="B3" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="C3" s="1">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1466,19 +2354,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>93</v>
+        <v>148</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>94</v>
+        <v>149</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
-      <c r="I3" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>95</v>
+      <c r="I3" s="1">
+        <v>0</v>
+      </c>
+      <c r="J3" s="1">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
